--- a/ig/DM-AVRIL-2026/ValueSet-jdv-traitement-suivi-cisis.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-jdv-traitement-suivi-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -155,7 +155,7 @@
     <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R66-CategorieEtablissement/FHIR/TRE-R66-CategorieEtablissement</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice</t>
   </si>
 </sst>
 </file>
